--- a/Dashboards/data/Data final/ingresos/inglab_series.xlsx
+++ b/Dashboards/data/Data final/ingresos/inglab_series.xlsx
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>439.25</v>
+        <v>438.23</v>
       </c>
     </row>
     <row r="54">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>76.87</v>
+        <v>78.20999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>462.76</v>
+        <v>471.35</v>
       </c>
     </row>
     <row r="57">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>79.72</v>
+        <v>80.52</v>
       </c>
     </row>
     <row r="58">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>462.36</v>
+        <v>460.61</v>
       </c>
     </row>
     <row r="60">
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>77.92</v>
+        <v>78.17</v>
       </c>
     </row>
     <row r="61">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>463.82</v>
+        <v>447.25</v>
       </c>
     </row>
     <row r="63">
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>77.17</v>
+        <v>73.61</v>
       </c>
     </row>
     <row r="64">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>483</v>
+        <v>514.4299999999999</v>
       </c>
     </row>
     <row r="66">
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>80.16</v>
+        <v>84.81999999999999</v>
       </c>
     </row>
     <row r="67">
